--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
@@ -6328,7 +6328,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
@@ -6328,7 +6328,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
@@ -6328,7 +6328,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
@@ -6328,7 +6328,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
@@ -6328,7 +6328,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
@@ -6328,7 +6328,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260609_213120.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
